--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356296</v>
+        <v>113356733</v>
       </c>
       <c r="B2" t="n">
-        <v>55984</v>
+        <v>97231</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755644</v>
+        <v>755658</v>
       </c>
       <c r="R2" t="n">
-        <v>7200477</v>
+        <v>7200462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356475</v>
+        <v>113356476</v>
       </c>
       <c r="B3" t="n">
-        <v>96261</v>
+        <v>96277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755647</v>
+        <v>755784</v>
       </c>
       <c r="R3" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356476</v>
+        <v>113356475</v>
       </c>
       <c r="B4" t="n">
-        <v>96261</v>
+        <v>96277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755784</v>
+        <v>755647</v>
       </c>
       <c r="R4" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356733</v>
+        <v>113356296</v>
       </c>
       <c r="B5" t="n">
-        <v>97215</v>
+        <v>55984</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755658</v>
+        <v>755644</v>
       </c>
       <c r="R5" t="n">
-        <v>7200462</v>
+        <v>7200477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356724</v>
+        <v>113356417</v>
       </c>
       <c r="B6" t="n">
-        <v>97215</v>
+        <v>96277</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755784</v>
+        <v>755757</v>
       </c>
       <c r="R6" t="n">
-        <v>7200647</v>
+        <v>7200661</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,12 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1213,7 @@
         <v>113356725</v>
       </c>
       <c r="B7" t="n">
-        <v>97215</v>
+        <v>97231</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356417</v>
+        <v>113356724</v>
       </c>
       <c r="B8" t="n">
-        <v>96261</v>
+        <v>97231</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755757</v>
+        <v>755784</v>
       </c>
       <c r="R8" t="n">
-        <v>7200661</v>
+        <v>7200647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97215</v>
+        <v>97231</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356733</v>
+        <v>113356476</v>
       </c>
       <c r="B2" t="n">
-        <v>97231</v>
+        <v>96277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755658</v>
+        <v>755784</v>
       </c>
       <c r="R2" t="n">
-        <v>7200462</v>
+        <v>7200647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356476</v>
+        <v>113356296</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>55984</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755784</v>
+        <v>755644</v>
       </c>
       <c r="R3" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356475</v>
+        <v>113356725</v>
       </c>
       <c r="B4" t="n">
-        <v>96277</v>
+        <v>97231</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755647</v>
+        <v>755744</v>
       </c>
       <c r="R4" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356296</v>
+        <v>113356733</v>
       </c>
       <c r="B5" t="n">
-        <v>55984</v>
+        <v>97231</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755644</v>
+        <v>755658</v>
       </c>
       <c r="R5" t="n">
-        <v>7200477</v>
+        <v>7200462</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356417</v>
+        <v>113356475</v>
       </c>
       <c r="B6" t="n">
         <v>96277</v>
@@ -1144,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755757</v>
+        <v>755647</v>
       </c>
       <c r="R6" t="n">
-        <v>7200661</v>
+        <v>7200477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356725</v>
+        <v>113356417</v>
       </c>
       <c r="B7" t="n">
-        <v>97231</v>
+        <v>96277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755744</v>
+        <v>755757</v>
       </c>
       <c r="R7" t="n">
-        <v>7200692</v>
+        <v>7200661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356476</v>
+        <v>113356475</v>
       </c>
       <c r="B2" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755784</v>
+        <v>755647</v>
       </c>
       <c r="R2" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356296</v>
+        <v>113356725</v>
       </c>
       <c r="B3" t="n">
-        <v>55984</v>
+        <v>97243</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755644</v>
+        <v>755744</v>
       </c>
       <c r="R3" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sågs flygande</t>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356725</v>
+        <v>113356724</v>
       </c>
       <c r="B4" t="n">
-        <v>97231</v>
+        <v>97243</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755744</v>
+        <v>755784</v>
       </c>
       <c r="R4" t="n">
-        <v>7200692</v>
+        <v>7200647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -962,17 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356733</v>
+        <v>113356296</v>
       </c>
       <c r="B5" t="n">
-        <v>97231</v>
+        <v>55985</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1043,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755658</v>
+        <v>755644</v>
       </c>
       <c r="R5" t="n">
-        <v>7200462</v>
+        <v>7200477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356475</v>
+        <v>113356476</v>
       </c>
       <c r="B6" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755647</v>
+        <v>755784</v>
       </c>
       <c r="R6" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1218,7 +1218,7 @@
         <v>113356417</v>
       </c>
       <c r="B7" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356724</v>
+        <v>113356733</v>
       </c>
       <c r="B8" t="n">
-        <v>97231</v>
+        <v>97243</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755784</v>
+        <v>755658</v>
       </c>
       <c r="R8" t="n">
-        <v>7200647</v>
+        <v>7200462</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97231</v>
+        <v>97243</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356475</v>
+        <v>113356417</v>
       </c>
       <c r="B2" t="n">
         <v>96289</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755647</v>
+        <v>755757</v>
       </c>
       <c r="R2" t="n">
-        <v>7200477</v>
+        <v>7200661</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356724</v>
+        <v>113356476</v>
       </c>
       <c r="B4" t="n">
-        <v>97243</v>
+        <v>96289</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1109,7 +1109,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356476</v>
+        <v>113356475</v>
       </c>
       <c r="B6" t="n">
         <v>96289</v>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755784</v>
+        <v>755647</v>
       </c>
       <c r="R6" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356417</v>
+        <v>113356724</v>
       </c>
       <c r="B7" t="n">
-        <v>96289</v>
+        <v>97243</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755757</v>
+        <v>755784</v>
       </c>
       <c r="R7" t="n">
-        <v>7200661</v>
+        <v>7200647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356417</v>
+        <v>113356476</v>
       </c>
       <c r="B2" t="n">
-        <v>96289</v>
+        <v>96311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755757</v>
+        <v>755784</v>
       </c>
       <c r="R2" t="n">
-        <v>7200661</v>
+        <v>7200647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356725</v>
+        <v>113356296</v>
       </c>
       <c r="B3" t="n">
-        <v>97243</v>
+        <v>55985</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755744</v>
+        <v>755644</v>
       </c>
       <c r="R3" t="n">
-        <v>7200692</v>
+        <v>7200477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ett 20-tal</t>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356476</v>
+        <v>113356733</v>
       </c>
       <c r="B4" t="n">
-        <v>96289</v>
+        <v>97265</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755784</v>
+        <v>755658</v>
       </c>
       <c r="R4" t="n">
-        <v>7200647</v>
+        <v>7200462</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356296</v>
+        <v>113356417</v>
       </c>
       <c r="B5" t="n">
-        <v>55985</v>
+        <v>96311</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755644</v>
+        <v>755757</v>
       </c>
       <c r="R5" t="n">
-        <v>7200477</v>
+        <v>7200661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,11 +1074,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356475</v>
+        <v>113356724</v>
       </c>
       <c r="B6" t="n">
-        <v>96289</v>
+        <v>97265</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755647</v>
+        <v>755784</v>
       </c>
       <c r="R6" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,12 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356724</v>
+        <v>113356725</v>
       </c>
       <c r="B7" t="n">
-        <v>97243</v>
+        <v>97265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755784</v>
+        <v>755744</v>
       </c>
       <c r="R7" t="n">
-        <v>7200647</v>
+        <v>7200692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1280,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356733</v>
+        <v>113356475</v>
       </c>
       <c r="B8" t="n">
-        <v>97243</v>
+        <v>96311</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755658</v>
+        <v>755647</v>
       </c>
       <c r="R8" t="n">
-        <v>7200462</v>
+        <v>7200477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97243</v>
+        <v>97265</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356476</v>
+        <v>113356475</v>
       </c>
       <c r="B2" t="n">
-        <v>96311</v>
+        <v>96315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755784</v>
+        <v>755647</v>
       </c>
       <c r="R2" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356296</v>
+        <v>113356725</v>
       </c>
       <c r="B3" t="n">
-        <v>55985</v>
+        <v>97269</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755644</v>
+        <v>755744</v>
       </c>
       <c r="R3" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,7 +861,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Sågs flygande</t>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356733</v>
+        <v>113356476</v>
       </c>
       <c r="B4" t="n">
-        <v>97265</v>
+        <v>96315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755658</v>
+        <v>755784</v>
       </c>
       <c r="R4" t="n">
-        <v>7200462</v>
+        <v>7200647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356417</v>
+        <v>113356296</v>
       </c>
       <c r="B5" t="n">
-        <v>96311</v>
+        <v>55988</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1014,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755757</v>
+        <v>755644</v>
       </c>
       <c r="R5" t="n">
-        <v>7200661</v>
+        <v>7200477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1074,6 +1074,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356724</v>
+        <v>113356733</v>
       </c>
       <c r="B6" t="n">
-        <v>97265</v>
+        <v>97269</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755784</v>
+        <v>755658</v>
       </c>
       <c r="R6" t="n">
-        <v>7200647</v>
+        <v>7200462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1174,12 +1179,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356725</v>
+        <v>113356417</v>
       </c>
       <c r="B7" t="n">
-        <v>97265</v>
+        <v>96315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755744</v>
+        <v>755757</v>
       </c>
       <c r="R7" t="n">
-        <v>7200692</v>
+        <v>7200661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356475</v>
+        <v>113356724</v>
       </c>
       <c r="B8" t="n">
-        <v>96311</v>
+        <v>97269</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755647</v>
+        <v>755784</v>
       </c>
       <c r="R8" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97265</v>
+        <v>97269</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356475</v>
+        <v>113356725</v>
       </c>
       <c r="B2" t="n">
-        <v>96315</v>
+        <v>97269</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755647</v>
+        <v>755744</v>
       </c>
       <c r="R2" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356725</v>
+        <v>113356417</v>
       </c>
       <c r="B3" t="n">
-        <v>97269</v>
+        <v>96315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755744</v>
+        <v>755757</v>
       </c>
       <c r="R3" t="n">
-        <v>7200692</v>
+        <v>7200661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,11 +862,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356476</v>
+        <v>113356296</v>
       </c>
       <c r="B4" t="n">
-        <v>96315</v>
+        <v>55988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755784</v>
+        <v>755644</v>
       </c>
       <c r="R4" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,6 +968,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,10 +1003,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356296</v>
+        <v>113356475</v>
       </c>
       <c r="B5" t="n">
-        <v>55988</v>
+        <v>96315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1014,21 +1019,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1038,7 +1043,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755644</v>
+        <v>755647</v>
       </c>
       <c r="R5" t="n">
         <v>7200477</v>
@@ -1074,11 +1079,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1109,10 +1109,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356733</v>
+        <v>113356476</v>
       </c>
       <c r="B6" t="n">
-        <v>97269</v>
+        <v>96315</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1125,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1149,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755658</v>
+        <v>755784</v>
       </c>
       <c r="R6" t="n">
-        <v>7200462</v>
+        <v>7200647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356417</v>
+        <v>113356724</v>
       </c>
       <c r="B7" t="n">
-        <v>96315</v>
+        <v>97269</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755757</v>
+        <v>755784</v>
       </c>
       <c r="R7" t="n">
-        <v>7200661</v>
+        <v>7200647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1285,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1321,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356724</v>
+        <v>113356733</v>
       </c>
       <c r="B8" t="n">
         <v>97269</v>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755784</v>
+        <v>755658</v>
       </c>
       <c r="R8" t="n">
-        <v>7200647</v>
+        <v>7200462</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356725</v>
+        <v>113356724</v>
       </c>
       <c r="B2" t="n">
-        <v>97269</v>
+        <v>97275</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755744</v>
+        <v>755784</v>
       </c>
       <c r="R2" t="n">
-        <v>7200692</v>
+        <v>7200647</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356417</v>
+        <v>113356475</v>
       </c>
       <c r="B3" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755757</v>
+        <v>755647</v>
       </c>
       <c r="R3" t="n">
-        <v>7200661</v>
+        <v>7200477</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -892,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356296</v>
+        <v>113356725</v>
       </c>
       <c r="B4" t="n">
-        <v>55988</v>
+        <v>97275</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -932,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755644</v>
+        <v>755744</v>
       </c>
       <c r="R4" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,7 +967,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sågs flygande</t>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356475</v>
+        <v>113356476</v>
       </c>
       <c r="B5" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1043,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755647</v>
+        <v>755784</v>
       </c>
       <c r="R5" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1109,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356476</v>
+        <v>113356733</v>
       </c>
       <c r="B6" t="n">
-        <v>96315</v>
+        <v>97275</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1125,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1149,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755784</v>
+        <v>755658</v>
       </c>
       <c r="R6" t="n">
-        <v>7200647</v>
+        <v>7200462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356724</v>
+        <v>113356417</v>
       </c>
       <c r="B7" t="n">
-        <v>97269</v>
+        <v>96321</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755784</v>
+        <v>755757</v>
       </c>
       <c r="R7" t="n">
-        <v>7200647</v>
+        <v>7200661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356733</v>
+        <v>113356296</v>
       </c>
       <c r="B8" t="n">
-        <v>97269</v>
+        <v>55992</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755658</v>
+        <v>755644</v>
       </c>
       <c r="R8" t="n">
-        <v>7200462</v>
+        <v>7200477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97269</v>
+        <v>97275</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356724</v>
+        <v>113356417</v>
       </c>
       <c r="B2" t="n">
-        <v>97275</v>
+        <v>96321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755784</v>
+        <v>755757</v>
       </c>
       <c r="R2" t="n">
-        <v>7200647</v>
+        <v>7200661</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356475</v>
+        <v>113356733</v>
       </c>
       <c r="B3" t="n">
-        <v>96321</v>
+        <v>97275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755647</v>
+        <v>755658</v>
       </c>
       <c r="R3" t="n">
-        <v>7200477</v>
+        <v>7200462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356725</v>
+        <v>113356475</v>
       </c>
       <c r="B4" t="n">
-        <v>97275</v>
+        <v>96321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755744</v>
+        <v>755647</v>
       </c>
       <c r="R4" t="n">
-        <v>7200692</v>
+        <v>7200477</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -963,11 +963,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356733</v>
+        <v>113356296</v>
       </c>
       <c r="B6" t="n">
-        <v>97275</v>
+        <v>55992</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755658</v>
+        <v>755644</v>
       </c>
       <c r="R6" t="n">
-        <v>7200462</v>
+        <v>7200477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,6 +1175,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356417</v>
+        <v>113356725</v>
       </c>
       <c r="B7" t="n">
-        <v>96321</v>
+        <v>97275</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755757</v>
+        <v>755744</v>
       </c>
       <c r="R7" t="n">
-        <v>7200661</v>
+        <v>7200692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,6 +1286,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356296</v>
+        <v>113356724</v>
       </c>
       <c r="B8" t="n">
-        <v>55992</v>
+        <v>97275</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1332,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755644</v>
+        <v>755784</v>
       </c>
       <c r="R8" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,17 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356417</v>
+        <v>113356733</v>
       </c>
       <c r="B2" t="n">
-        <v>96321</v>
+        <v>97282</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755757</v>
+        <v>755658</v>
       </c>
       <c r="R2" t="n">
-        <v>7200661</v>
+        <v>7200462</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356733</v>
+        <v>113356476</v>
       </c>
       <c r="B3" t="n">
-        <v>97275</v>
+        <v>96328</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755658</v>
+        <v>755784</v>
       </c>
       <c r="R3" t="n">
-        <v>7200462</v>
+        <v>7200647</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356475</v>
+        <v>113356724</v>
       </c>
       <c r="B4" t="n">
-        <v>96321</v>
+        <v>97282</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755647</v>
+        <v>755784</v>
       </c>
       <c r="R4" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356476</v>
+        <v>113356296</v>
       </c>
       <c r="B5" t="n">
-        <v>96321</v>
+        <v>55999</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755784</v>
+        <v>755644</v>
       </c>
       <c r="R5" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,6 +1069,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356296</v>
+        <v>113356725</v>
       </c>
       <c r="B6" t="n">
-        <v>55992</v>
+        <v>97282</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1120,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755644</v>
+        <v>755744</v>
       </c>
       <c r="R6" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1179,7 +1184,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sågs flygande</t>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356725</v>
+        <v>113356417</v>
       </c>
       <c r="B7" t="n">
-        <v>97275</v>
+        <v>96328</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1255,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755744</v>
+        <v>755757</v>
       </c>
       <c r="R7" t="n">
-        <v>7200692</v>
+        <v>7200661</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1291,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356724</v>
+        <v>113356475</v>
       </c>
       <c r="B8" t="n">
-        <v>97275</v>
+        <v>96328</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1337,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755784</v>
+        <v>755647</v>
       </c>
       <c r="R8" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97275</v>
+        <v>97282</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356733</v>
+        <v>113356475</v>
       </c>
       <c r="B2" t="n">
-        <v>97282</v>
+        <v>96333</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755658</v>
+        <v>755647</v>
       </c>
       <c r="R2" t="n">
-        <v>7200462</v>
+        <v>7200477</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356476</v>
+        <v>113356733</v>
       </c>
       <c r="B3" t="n">
-        <v>96328</v>
+        <v>97287</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755784</v>
+        <v>755658</v>
       </c>
       <c r="R3" t="n">
-        <v>7200647</v>
+        <v>7200462</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356724</v>
+        <v>113356417</v>
       </c>
       <c r="B4" t="n">
-        <v>97282</v>
+        <v>96333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755784</v>
+        <v>755757</v>
       </c>
       <c r="R4" t="n">
-        <v>7200647</v>
+        <v>7200661</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -957,12 +957,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356296</v>
+        <v>113356476</v>
       </c>
       <c r="B5" t="n">
-        <v>55999</v>
+        <v>96333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,21 +1009,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755644</v>
+        <v>755784</v>
       </c>
       <c r="R5" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1069,11 +1069,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1104,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356725</v>
+        <v>113356296</v>
       </c>
       <c r="B6" t="n">
-        <v>97282</v>
+        <v>56001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1120,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1144,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755744</v>
+        <v>755644</v>
       </c>
       <c r="R6" t="n">
-        <v>7200692</v>
+        <v>7200477</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1184,7 +1179,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ett 20-tal</t>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356417</v>
+        <v>113356724</v>
       </c>
       <c r="B7" t="n">
-        <v>96328</v>
+        <v>97287</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755757</v>
+        <v>755784</v>
       </c>
       <c r="R7" t="n">
-        <v>7200661</v>
+        <v>7200647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,12 +1280,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356475</v>
+        <v>113356725</v>
       </c>
       <c r="B8" t="n">
-        <v>96328</v>
+        <v>97287</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755647</v>
+        <v>755744</v>
       </c>
       <c r="R8" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1397,6 +1392,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97282</v>
+        <v>97287</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -1099,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356296</v>
+        <v>113356724</v>
       </c>
       <c r="B6" t="n">
-        <v>56001</v>
+        <v>97287</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1115,21 +1115,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755644</v>
+        <v>755784</v>
       </c>
       <c r="R6" t="n">
-        <v>7200477</v>
+        <v>7200647</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,17 +1169,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1210,10 +1205,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356724</v>
+        <v>113356296</v>
       </c>
       <c r="B7" t="n">
-        <v>97287</v>
+        <v>56001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1221,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1245,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755784</v>
+        <v>755644</v>
       </c>
       <c r="R7" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1280,12 +1275,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356475</v>
+        <v>113356296</v>
       </c>
       <c r="B2" t="n">
-        <v>96333</v>
+        <v>56029</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755647</v>
+        <v>755644</v>
       </c>
       <c r="R2" t="n">
         <v>7200477</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356733</v>
+        <v>113356417</v>
       </c>
       <c r="B3" t="n">
-        <v>97287</v>
+        <v>96361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755658</v>
+        <v>755757</v>
       </c>
       <c r="R3" t="n">
-        <v>7200462</v>
+        <v>7200661</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356417</v>
+        <v>113356476</v>
       </c>
       <c r="B4" t="n">
-        <v>96333</v>
+        <v>96361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +932,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>755757</v>
+        <v>755784</v>
       </c>
       <c r="R4" t="n">
-        <v>7200661</v>
+        <v>7200647</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,10 +998,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356476</v>
+        <v>113356475</v>
       </c>
       <c r="B5" t="n">
-        <v>96333</v>
+        <v>96361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1033,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755784</v>
+        <v>755647</v>
       </c>
       <c r="R5" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,10 +1104,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113356724</v>
+        <v>113356733</v>
       </c>
       <c r="B6" t="n">
-        <v>97287</v>
+        <v>97315</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,10 +1144,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>755784</v>
+        <v>755658</v>
       </c>
       <c r="R6" t="n">
-        <v>7200647</v>
+        <v>7200462</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1169,12 +1174,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356296</v>
+        <v>113356725</v>
       </c>
       <c r="B7" t="n">
-        <v>56001</v>
+        <v>97315</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1221,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>219790</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755644</v>
+        <v>755744</v>
       </c>
       <c r="R7" t="n">
-        <v>7200477</v>
+        <v>7200692</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sågs flygande</t>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,10 +1321,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356725</v>
+        <v>113356724</v>
       </c>
       <c r="B8" t="n">
-        <v>97287</v>
+        <v>97315</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1356,10 +1361,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755744</v>
+        <v>755784</v>
       </c>
       <c r="R8" t="n">
-        <v>7200692</v>
+        <v>7200647</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1386,17 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1573,7 +1573,7 @@
         <v>113356736</v>
       </c>
       <c r="B10" t="n">
-        <v>97287</v>
+        <v>97315</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356296</v>
+        <v>113356475</v>
       </c>
       <c r="B2" t="n">
-        <v>56029</v>
+        <v>96361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>755644</v>
+        <v>755647</v>
       </c>
       <c r="R2" t="n">
         <v>7200477</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -786,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356417</v>
+        <v>113356725</v>
       </c>
       <c r="B3" t="n">
-        <v>96361</v>
+        <v>97315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -826,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>755757</v>
+        <v>755744</v>
       </c>
       <c r="R3" t="n">
-        <v>7200661</v>
+        <v>7200692</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,6 +857,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,10 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356476</v>
+        <v>113356724</v>
       </c>
       <c r="B4" t="n">
-        <v>96361</v>
+        <v>97315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -908,21 +908,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,12 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-08-29</t>
+          <t>2023-10-26</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -998,7 +998,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356475</v>
+        <v>113356417</v>
       </c>
       <c r="B5" t="n">
         <v>96361</v>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>755647</v>
+        <v>755757</v>
       </c>
       <c r="R5" t="n">
-        <v>7200477</v>
+        <v>7200661</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1210,10 +1210,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113356725</v>
+        <v>113356476</v>
       </c>
       <c r="B7" t="n">
-        <v>97315</v>
+        <v>96361</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219790</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>755744</v>
+        <v>755784</v>
       </c>
       <c r="R7" t="n">
-        <v>7200692</v>
+        <v>7200647</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,11 +1286,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-29</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett 20-tal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,10 +1316,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113356724</v>
+        <v>113356296</v>
       </c>
       <c r="B8" t="n">
-        <v>97315</v>
+        <v>56029</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1337,21 +1332,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219790</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1361,10 +1356,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>755784</v>
+        <v>755644</v>
       </c>
       <c r="R8" t="n">
-        <v>7200647</v>
+        <v>7200477</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1391,12 +1386,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-26</t>
+          <t>2023-08-29</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Sågs flygande</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 30604-2020 artfynd.xlsx
+++ b/artfynd/A 30604-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
